--- a/numerical-workflows/v2/framework/经济/模块产销表/13_外循环_通行证.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/13_外循环_通行证.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$238</definedName>
@@ -672,7 +672,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>产出:23482.0；引用:20582.0</t>
+          <t>产出:23482.0；引用:19582.0</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -23808,7 +23808,7 @@
         <v>2</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F250" s="5" t="inlineStr"/>
       <c r="G250" s="5" t="inlineStr"/>
@@ -24348,7 +24348,7 @@
         <v>2</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F262" s="5" t="inlineStr"/>
       <c r="G262" s="5" t="inlineStr"/>
@@ -24888,7 +24888,7 @@
         <v>2</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F274" s="5" t="inlineStr"/>
       <c r="G274" s="5" t="inlineStr"/>
@@ -25428,7 +25428,7 @@
         <v>2</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F286" s="5" t="inlineStr"/>
       <c r="G286" s="5" t="inlineStr"/>
@@ -25968,7 +25968,7 @@
         <v>2</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F298" s="5" t="inlineStr"/>
       <c r="G298" s="5" t="inlineStr"/>
